--- a/addresses/mock_google_data/distance_matrices/05_distance_matrix_group-2.xlsx
+++ b/addresses/mock_google_data/distance_matrices/05_distance_matrix_group-2.xlsx
@@ -419,313 +419,313 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>אשל 5, רכסים</t>
+          <t>אשר לשלמה 1, מודיעין עילית</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>דקל 2, רכסים</t>
+          <t>הריטבא 8, מודיעין עילית</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>הדס 4, רכסים</t>
+          <t>חזון איש 7, מודיעין עילית</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>הדקל 30, רכסים</t>
+          <t>חזון איש 15, מודיעין עילית</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>הורדים 4, רכסים</t>
+          <t>חזון איש 23, מודיעין עילית</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>הכלניות 1, רכסים</t>
+          <t>חזון איש 26, מודיעין עילית</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>הכלניות 32, רכסים</t>
+          <t>חזון דוד 17, מודיעין עילית</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>הכלניות 47, רכסים</t>
+          <t>חזון דוד 25, מודיעין עילית</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>הנרקיסים 24, רכסים</t>
+          <t>חפץ חיים 21, מודיעין עילית</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>הרב קוק 12, רכסים</t>
+          <t>מסילת יוסף 14, מודיעין עילית</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>הרב קוק 26, רכסים</t>
+          <t>מסילת יוסף 19, מודיעין עילית</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>הרימונים 16, רכסים</t>
+          <t>מרומי שדה 3, מודיעין עילית</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>השקד 13, רכסים</t>
+          <t>נתיבות המשפט 59, מודיעין עילית</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>השקד 14, רכסים</t>
+          <t>נתיבות המשפט 71, מודיעין עילית</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>השקד 40, רכסים</t>
+          <t>נתיבות המשפט 85, מודיעין עילית</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>השקד 59, רכסים</t>
+          <t>נתיבות המשפט 93, מודיעין עילית</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ורדים 5, רכסים</t>
+          <t>נתיבות המשפט 107, מודיעין עילית</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>חזון איש 8, רכסים</t>
+          <t>נתיבות שלום 11, מודיעין עילית</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>כלניות 17, רכסים</t>
+          <t>קצות החושן 8, מודיעין עילית</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>מעלה החזון איש 13, רכסים</t>
+          <t>קצות החושן 17, מודיעין עילית</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>רחוב הזית 13, רכסים</t>
+          <t>רמבם 18, מודיעין עילית</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>רחוב סביון 38, רכסים</t>
+          <t>שאגת אריה 1, מודיעין עילית</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>רימונים 15, רכסים</t>
+          <t>שערי תשובה 6, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>אשל 5, רכסים</t>
+          <t>אשר לשלמה 1, מודיעין עילית</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="n">
         <v>9</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="M2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
       <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" t="n">
         <v>9</v>
       </c>
-      <c r="Q2" t="n">
-        <v>9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>5</v>
-      </c>
-      <c r="S2" t="n">
-        <v>8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4</v>
-      </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>דקל 2, רכסים</t>
+          <t>הריטבא 8, מודיעין עילית</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
         <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V3" t="n">
         <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>הדס 4, רכסים</t>
+          <t>חזון איש 7, מודיעין עילית</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
         <v>8</v>
@@ -734,44 +734,44 @@
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
         <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>הדקל 30, רכסים</t>
+          <t>חזון איש 15, מודיעין עילית</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -780,235 +780,235 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>7</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7</v>
-      </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>הורדים 4, רכסים</t>
+          <t>חזון איש 23, מודיעין עילית</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>הכלניות 1, רכסים</t>
+          <t>חזון איש 26, מודיעין עילית</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>הכלניות 32, רכסים</t>
+          <t>חזון דוד 17, מודיעין עילית</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -1020,55 +1020,55 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>הכלניות 47, רכסים</t>
+          <t>חזון דוד 25, מודיעין עילית</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1078,16 +1078,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -1096,122 +1096,122 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
         <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>הנרקיסים 24, רכסים</t>
+          <t>חפץ חיים 21, מודיעין עילית</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
         <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X10" t="n">
         <v>4</v>
@@ -1220,190 +1220,190 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>הרב קוק 12, רכסים</t>
+          <t>מסילת יוסף 14, מודיעין עילית</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
         <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
         <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>הרב קוק 26, רכסים</t>
+          <t>מסילת יוסף 19, מודיעין עילית</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>הרימונים 16, רכסים</t>
+          <t>מרומי שדה 3, מודיעין עילית</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -1412,68 +1412,68 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
         <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>השקד 13, רכסים</t>
+          <t>נתיבות המשפט 59, מודיעין עילית</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -1482,10 +1482,10 @@
         <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1494,44 +1494,44 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
         <v>5</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>השקד 14, רכסים</t>
+          <t>נתיבות המשפט 71, מודיעין עילית</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -1540,25 +1540,25 @@
         <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
@@ -1573,13 +1573,13 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
         <v>3</v>
@@ -1588,59 +1588,59 @@
         <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>השקד 40, רכסים</t>
+          <t>נתיבות המשפט 85, מודיעין עילית</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1649,110 +1649,110 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>השקד 59, רכסים</t>
+          <t>נתיבות המשפט 93, מודיעין עילית</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ורדים 5, רכסים</t>
+          <t>נתיבות המשפט 107, מודיעין עילית</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1762,92 +1762,92 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>חזון איש 8, רכסים</t>
+          <t>נתיבות שלום 11, מודיעין עילית</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
         <v>5</v>
@@ -1856,122 +1856,122 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>כלניות 17, רכסים</t>
+          <t>קצות החושן 8, מודיעין עילית</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>3</v>
@@ -1980,47 +1980,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>מעלה החזון איש 13, רכסים</t>
+          <t>קצות החושן 17, מודיעין עילית</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2029,159 +2029,159 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>רחוב הזית 13, רכסים</t>
+          <t>רמבם 18, מודיעין עילית</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
         <v>7</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>רחוב סביון 38, רכסים</t>
+          <t>שאגת אריה 1, מודיעין עילית</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
         <v>3</v>
@@ -2190,95 +2190,95 @@
         <v>7</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>רימונים 15, רכסים</t>
+          <t>שערי תשובה 6, מודיעין עילית</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
